--- a/backend/static/plantilla_residentes.xlsx
+++ b/backend/static/plantilla_residentes.xlsx
@@ -270,6 +270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:dimension ref="A1:D501"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
